--- a/Admin_Master.xlsx
+++ b/Admin_Master.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7035"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -25,14 +25,14 @@
     <t>admin</t>
   </si>
   <si>
-    <t>admin123</t>
+    <t>New@842293</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -44,6 +44,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -66,10 +74,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -77,8 +86,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -396,11 +409,14 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>